--- a/data/crit_values_final.xlsx
+++ b/data/crit_values_final.xlsx
@@ -178,19 +178,19 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>43.7</v>
+        <v>43.2</v>
       </c>
       <c r="C2" t="n">
-        <v>47.6</v>
+        <v>47.3</v>
       </c>
       <c r="D2" t="n">
         <v>51.1</v>
       </c>
       <c r="E2" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
       <c r="F2" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="G2" t="n">
         <v>52.5</v>
@@ -199,10 +199,10 @@
         <v>53.4</v>
       </c>
       <c r="I2" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="J2" t="n">
-        <v>58.4</v>
+        <v>58.9</v>
       </c>
       <c r="K2" t="n" s="2">
         <v>44733.0</v>
@@ -216,31 +216,31 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>42.3</v>
+        <v>41.3</v>
       </c>
       <c r="C3" t="n">
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
       <c r="D3" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="E3" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F3" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="G3" t="n">
-        <v>53.2</v>
+        <v>53.7</v>
       </c>
       <c r="H3" t="n">
-        <v>55.3</v>
+        <v>55.0</v>
       </c>
       <c r="I3" t="n">
-        <v>58.4</v>
+        <v>58.8</v>
       </c>
       <c r="J3" t="n">
-        <v>62.0</v>
+        <v>63.5</v>
       </c>
       <c r="K3" t="n" s="2">
         <v>44733.0</v>
@@ -260,10 +260,10 @@
         <v>44.3</v>
       </c>
       <c r="D4" t="n">
-        <v>47.0</v>
+        <v>46.7</v>
       </c>
       <c r="E4" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F4" t="n">
         <v>51.9</v>
@@ -272,13 +272,13 @@
         <v>53.5</v>
       </c>
       <c r="H4" t="n">
-        <v>54.4</v>
+        <v>54.7</v>
       </c>
       <c r="I4" t="n">
         <v>58.7</v>
       </c>
       <c r="J4" t="n">
-        <v>62.7</v>
+        <v>62.9</v>
       </c>
       <c r="K4" t="n" s="2">
         <v>44733.0</v>
@@ -292,13 +292,13 @@
         <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="C5" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="D5" t="n">
-        <v>44.7</v>
+        <v>45.2</v>
       </c>
       <c r="E5" t="n">
         <v>50.9</v>
@@ -307,16 +307,16 @@
         <v>52.0</v>
       </c>
       <c r="G5" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="H5" t="n">
-        <v>57.2</v>
+        <v>57.0</v>
       </c>
       <c r="I5" t="n">
-        <v>60.5</v>
+        <v>60.4</v>
       </c>
       <c r="J5" t="n">
-        <v>64.1</v>
+        <v>63.9</v>
       </c>
       <c r="K5" t="n" s="2">
         <v>44733.0</v>
@@ -336,10 +336,10 @@
         <v>43.5</v>
       </c>
       <c r="D6" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="E6" t="n">
-        <v>51.2</v>
+        <v>51.0</v>
       </c>
       <c r="F6" t="n">
         <v>52.4</v>
@@ -348,13 +348,13 @@
         <v>54.1</v>
       </c>
       <c r="H6" t="n">
-        <v>56.9</v>
+        <v>56.2</v>
       </c>
       <c r="I6" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="J6" t="n">
-        <v>63.4</v>
+        <v>64.3</v>
       </c>
       <c r="K6" t="n" s="2">
         <v>44733.0</v>
@@ -368,31 +368,31 @@
         <v>17</v>
       </c>
       <c r="B7" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="C7" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="D7" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="E7" t="n">
         <v>49.7</v>
       </c>
       <c r="F7" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="G7" t="n">
-        <v>52.0</v>
+        <v>52.2</v>
       </c>
       <c r="H7" t="n">
         <v>53.7</v>
       </c>
       <c r="I7" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
       <c r="J7" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="K7" t="n" s="2">
         <v>44733.0</v>
@@ -406,13 +406,13 @@
         <v>18</v>
       </c>
       <c r="B8" t="n">
-        <v>41.8</v>
+        <v>42.3</v>
       </c>
       <c r="C8" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="D8" t="n">
-        <v>47.0</v>
+        <v>46.7</v>
       </c>
       <c r="E8" t="n">
         <v>50.0</v>
@@ -421,16 +421,16 @@
         <v>51.0</v>
       </c>
       <c r="G8" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="H8" t="n">
-        <v>52.7</v>
+        <v>53.2</v>
       </c>
       <c r="I8" t="n">
         <v>56.7</v>
       </c>
       <c r="J8" t="n">
-        <v>60.2</v>
+        <v>60.4</v>
       </c>
       <c r="K8" t="n" s="2">
         <v>44733.0</v>
@@ -444,31 +444,31 @@
         <v>19</v>
       </c>
       <c r="B9" t="n">
-        <v>40.0</v>
+        <v>40.3</v>
       </c>
       <c r="C9" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="D9" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="E9" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F9" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="G9" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
       <c r="H9" t="n">
-        <v>56.9</v>
+        <v>57.2</v>
       </c>
       <c r="I9" t="n">
-        <v>59.6</v>
+        <v>59.9</v>
       </c>
       <c r="J9" t="n">
-        <v>62.0</v>
+        <v>62.4</v>
       </c>
       <c r="K9" t="n" s="2">
         <v>44733.0</v>
@@ -488,25 +488,25 @@
         <v>46.5</v>
       </c>
       <c r="D10" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="E10" t="n">
         <v>52.8</v>
       </c>
       <c r="F10" t="n">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
       <c r="G10" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="H10" t="n">
-        <v>58.4</v>
+        <v>57.8</v>
       </c>
       <c r="I10" t="n">
-        <v>61.0</v>
+        <v>60.8</v>
       </c>
       <c r="J10" t="n">
-        <v>63.2</v>
+        <v>63.6</v>
       </c>
       <c r="K10" t="n" s="2">
         <v>44733.0</v>
@@ -520,31 +520,31 @@
         <v>21</v>
       </c>
       <c r="B11" t="n">
-        <v>40.0</v>
+        <v>39.8</v>
       </c>
       <c r="C11" t="n">
-        <v>43.7</v>
+        <v>44.0</v>
       </c>
       <c r="D11" t="n">
-        <v>47.7</v>
+        <v>48.2</v>
       </c>
       <c r="E11" t="n">
-        <v>52.3</v>
+        <v>51.9</v>
       </c>
       <c r="F11" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="G11" t="n">
-        <v>54.9</v>
+        <v>55.2</v>
       </c>
       <c r="H11" t="n">
         <v>58.6</v>
       </c>
       <c r="I11" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
       <c r="J11" t="n">
-        <v>66.5</v>
+        <v>65.9</v>
       </c>
       <c r="K11" t="n" s="2">
         <v>44733.0</v>
@@ -558,31 +558,31 @@
         <v>22</v>
       </c>
       <c r="B12" t="n">
-        <v>34.1</v>
+        <v>34.8</v>
       </c>
       <c r="C12" t="n">
-        <v>40.3</v>
+        <v>40.6</v>
       </c>
       <c r="D12" t="n">
         <v>46.2</v>
       </c>
       <c r="E12" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="F12" t="n">
         <v>48.9</v>
       </c>
       <c r="G12" t="n">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
       <c r="H12" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="I12" t="n">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
       <c r="J12" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="K12" t="n" s="2">
         <v>44733.0</v>
@@ -599,13 +599,13 @@
         <v>43.2</v>
       </c>
       <c r="C13" t="n">
-        <v>46.0</v>
+        <v>46.1</v>
       </c>
       <c r="D13" t="n">
         <v>49.2</v>
       </c>
       <c r="E13" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F13" t="n">
         <v>52.5</v>
@@ -614,13 +614,13 @@
         <v>54.2</v>
       </c>
       <c r="H13" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="I13" t="n">
-        <v>58.4</v>
+        <v>58.2</v>
       </c>
       <c r="J13" t="n">
-        <v>62.3</v>
+        <v>62.8</v>
       </c>
       <c r="K13" t="n" s="2">
         <v>44768.0</v>
@@ -634,10 +634,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>45.4</v>
+        <v>45.7</v>
       </c>
       <c r="C14" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="D14" t="n">
         <v>49.7</v>
@@ -649,16 +649,16 @@
         <v>53.2</v>
       </c>
       <c r="G14" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="H14" t="n">
         <v>54.9</v>
       </c>
       <c r="I14" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
       <c r="J14" t="n">
-        <v>62.0</v>
+        <v>61.9</v>
       </c>
       <c r="K14" t="n" s="2">
         <v>44768.0</v>
@@ -672,19 +672,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>45.0</v>
+        <v>45.2</v>
       </c>
       <c r="C15" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="D15" t="n">
         <v>50.2</v>
       </c>
       <c r="E15" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="F15" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
       <c r="G15" t="n">
         <v>54.1</v>
@@ -693,7 +693,7 @@
         <v>54.6</v>
       </c>
       <c r="I15" t="n">
-        <v>57.2</v>
+        <v>57.1</v>
       </c>
       <c r="J15" t="n">
         <v>60.5</v>
@@ -710,31 +710,31 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>44.7</v>
+        <v>44.2</v>
       </c>
       <c r="C16" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="D16" t="n">
         <v>51.1</v>
       </c>
       <c r="E16" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="F16" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="G16" t="n">
-        <v>54.7</v>
+        <v>54.9</v>
       </c>
       <c r="H16" t="n">
-        <v>54.7</v>
+        <v>54.5</v>
       </c>
       <c r="I16" t="n">
-        <v>58.8</v>
+        <v>59.0</v>
       </c>
       <c r="J16" t="n">
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
       <c r="K16" t="n" s="2">
         <v>44768.0</v>
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>44.7</v>
+        <v>44.2</v>
       </c>
       <c r="C17" t="n">
         <v>46.2</v>
@@ -757,22 +757,22 @@
         <v>48.7</v>
       </c>
       <c r="E17" t="n">
-        <v>53.4</v>
+        <v>52.9</v>
       </c>
       <c r="F17" t="n">
-        <v>54.5</v>
+        <v>54.3</v>
       </c>
       <c r="G17" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="H17" t="n">
-        <v>60.0</v>
+        <v>58.2</v>
       </c>
       <c r="I17" t="n">
-        <v>61.9</v>
+        <v>61.6</v>
       </c>
       <c r="J17" t="n">
-        <v>64.0</v>
+        <v>64.2</v>
       </c>
       <c r="K17" t="n" s="2">
         <v>44768.0</v>
@@ -786,31 +786,31 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>41.3</v>
+        <v>41.8</v>
       </c>
       <c r="C18" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="D18" t="n">
-        <v>46.7</v>
+        <v>47.2</v>
       </c>
       <c r="E18" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="F18" t="n">
         <v>52.5</v>
       </c>
       <c r="G18" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
       <c r="H18" t="n">
-        <v>57.4</v>
+        <v>57.2</v>
       </c>
       <c r="I18" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
       <c r="J18" t="n">
-        <v>63.3</v>
+        <v>62.5</v>
       </c>
       <c r="K18" t="n" s="2">
         <v>44768.0</v>
@@ -827,22 +827,22 @@
         <v>47.2</v>
       </c>
       <c r="C19" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="D19" t="n">
         <v>50.2</v>
       </c>
       <c r="E19" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F19" t="n">
         <v>51.8</v>
       </c>
       <c r="G19" t="n">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
       <c r="H19" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
       <c r="I19" t="n">
         <v>54.7</v>
@@ -862,31 +862,31 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>42.0</v>
+        <v>41.8</v>
       </c>
       <c r="C20" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="D20" t="n">
-        <v>48.9</v>
+        <v>49.7</v>
       </c>
       <c r="E20" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="F20" t="n">
-        <v>52.0</v>
+        <v>52.2</v>
       </c>
       <c r="G20" t="n">
-        <v>53.3</v>
+        <v>53.7</v>
       </c>
       <c r="H20" t="n">
         <v>54.4</v>
       </c>
       <c r="I20" t="n">
-        <v>57.3</v>
+        <v>57.6</v>
       </c>
       <c r="J20" t="n">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
       <c r="K20" t="n" s="2">
         <v>44768.0</v>
@@ -900,31 +900,31 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>39.3</v>
+        <v>37.8</v>
       </c>
       <c r="C21" t="n">
-        <v>44.0</v>
+        <v>44.1</v>
       </c>
       <c r="D21" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="E21" t="n">
-        <v>54.5</v>
+        <v>54.3</v>
       </c>
       <c r="F21" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="G21" t="n">
-        <v>59.4</v>
+        <v>59.7</v>
       </c>
       <c r="H21" t="n">
-        <v>61.2</v>
+        <v>60.6</v>
       </c>
       <c r="I21" t="n">
-        <v>67.2</v>
+        <v>66.7</v>
       </c>
       <c r="J21" t="n">
-        <v>76.0</v>
+        <v>77.9</v>
       </c>
       <c r="K21" t="n" s="2">
         <v>44768.0</v>
@@ -938,10 +938,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>37.6</v>
+        <v>36.8</v>
       </c>
       <c r="C22" t="n">
-        <v>44.2</v>
+        <v>43.9</v>
       </c>
       <c r="D22" t="n">
         <v>47.7</v>
@@ -950,19 +950,19 @@
         <v>52.0</v>
       </c>
       <c r="F22" t="n">
-        <v>52.9</v>
+        <v>53.0</v>
       </c>
       <c r="G22" t="n">
-        <v>54.9</v>
+        <v>55.2</v>
       </c>
       <c r="H22" t="n">
-        <v>56.9</v>
+        <v>56.6</v>
       </c>
       <c r="I22" t="n">
-        <v>60.4</v>
+        <v>60.9</v>
       </c>
       <c r="J22" t="n">
-        <v>69.0</v>
+        <v>70.4</v>
       </c>
       <c r="K22" t="n" s="2">
         <v>44768.0</v>
@@ -976,31 +976,31 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>43.7</v>
+        <v>43.2</v>
       </c>
       <c r="C23" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
       <c r="D23" t="n">
         <v>50.6</v>
       </c>
       <c r="E23" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="F23" t="n">
         <v>53.5</v>
       </c>
       <c r="G23" t="n">
-        <v>55.1</v>
+        <v>54.8</v>
       </c>
       <c r="H23" t="n">
-        <v>55.7</v>
+        <v>55.3</v>
       </c>
       <c r="I23" t="n">
-        <v>59.0</v>
+        <v>59.1</v>
       </c>
       <c r="J23" t="n">
-        <v>62.3</v>
+        <v>63.1</v>
       </c>
       <c r="K23" t="n" s="2">
         <v>44768.0</v>
@@ -1017,28 +1017,28 @@
         <v>37.8</v>
       </c>
       <c r="C24" t="n">
-        <v>41.3</v>
+        <v>41.6</v>
       </c>
       <c r="D24" t="n">
-        <v>44.2</v>
+        <v>45.2</v>
       </c>
       <c r="E24" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="F24" t="n">
         <v>49.1</v>
       </c>
       <c r="G24" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="H24" t="n">
-        <v>53.0</v>
+        <v>52.3</v>
       </c>
       <c r="I24" t="n">
-        <v>56.1</v>
+        <v>55.7</v>
       </c>
       <c r="J24" t="n">
-        <v>59.6</v>
+        <v>60.2</v>
       </c>
       <c r="K24" t="n" s="2">
         <v>45063.0</v>
@@ -1052,28 +1052,28 @@
         <v>14</v>
       </c>
       <c r="B25" t="n">
-        <v>38.0</v>
+        <v>37.8</v>
       </c>
       <c r="C25" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="D25" t="n">
-        <v>45.7</v>
+        <v>46.2</v>
       </c>
       <c r="E25" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
       <c r="F25" t="n">
         <v>48.6</v>
       </c>
       <c r="G25" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="H25" t="n">
         <v>50.1</v>
       </c>
-      <c r="H25" t="n">
-        <v>50.4</v>
-      </c>
       <c r="I25" t="n">
-        <v>54.2</v>
+        <v>54.0</v>
       </c>
       <c r="J25" t="n">
         <v>59.5</v>
@@ -1090,31 +1090,31 @@
         <v>17</v>
       </c>
       <c r="B26" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="C26" t="n">
-        <v>39.9</v>
+        <v>40.2</v>
       </c>
       <c r="D26" t="n">
-        <v>43.0</v>
+        <v>43.2</v>
       </c>
       <c r="E26" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="F26" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="G26" t="n">
         <v>51.0</v>
       </c>
       <c r="H26" t="n">
-        <v>55.5</v>
+        <v>54.6</v>
       </c>
       <c r="I26" t="n">
-        <v>58.5</v>
+        <v>58.1</v>
       </c>
       <c r="J26" t="n">
-        <v>62.1</v>
+        <v>62.6</v>
       </c>
       <c r="K26" t="n" s="2">
         <v>45063.0</v>
@@ -1128,31 +1128,31 @@
         <v>12</v>
       </c>
       <c r="B27" t="n">
-        <v>42.7</v>
+        <v>42.3</v>
       </c>
       <c r="C27" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="D27" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="E27" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="F27" t="n">
         <v>48.8</v>
       </c>
       <c r="G27" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="H27" t="n">
-        <v>50.0</v>
+        <v>49.4</v>
       </c>
       <c r="I27" t="n">
-        <v>52.0</v>
+        <v>51.9</v>
       </c>
       <c r="J27" t="n">
-        <v>53.7</v>
+        <v>54.2</v>
       </c>
       <c r="K27" t="n" s="2">
         <v>45077.0</v>
@@ -1169,7 +1169,7 @@
         <v>42.3</v>
       </c>
       <c r="C28" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="D28" t="n">
         <v>45.2</v>
@@ -1181,13 +1181,13 @@
         <v>48.4</v>
       </c>
       <c r="G28" t="n">
-        <v>49.0</v>
+        <v>49.1</v>
       </c>
       <c r="H28" t="n">
-        <v>51.0</v>
+        <v>50.9</v>
       </c>
       <c r="I28" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="J28" t="n">
         <v>54.1</v>
@@ -1207,10 +1207,10 @@
         <v>38.3</v>
       </c>
       <c r="C29" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="D29" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="E29" t="n">
         <v>48.4</v>
@@ -1219,16 +1219,16 @@
         <v>49.3</v>
       </c>
       <c r="G29" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="H29" t="n">
-        <v>55.3</v>
+        <v>55.1</v>
       </c>
       <c r="I29" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="J29" t="n">
-        <v>59.2</v>
+        <v>58.9</v>
       </c>
       <c r="K29" t="n" s="2">
         <v>45077.0</v>
@@ -1245,10 +1245,10 @@
         <v>41.3</v>
       </c>
       <c r="C30" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="D30" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="E30" t="n">
         <v>48.0</v>
@@ -1257,16 +1257,16 @@
         <v>49.2</v>
       </c>
       <c r="G30" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="H30" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
       <c r="I30" t="n">
-        <v>54.0</v>
+        <v>54.2</v>
       </c>
       <c r="J30" t="n">
-        <v>55.7</v>
+        <v>55.9</v>
       </c>
       <c r="K30" t="n" s="2">
         <v>45090.0</v>
@@ -1280,31 +1280,31 @@
         <v>13</v>
       </c>
       <c r="B31" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="C31" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="D31" t="n">
         <v>45.7</v>
       </c>
       <c r="E31" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F31" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="G31" t="n">
         <v>51.1</v>
       </c>
       <c r="H31" t="n">
-        <v>55.4</v>
+        <v>55.6</v>
       </c>
       <c r="I31" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="J31" t="n">
-        <v>59.4</v>
+        <v>59.6</v>
       </c>
       <c r="K31" t="n" s="2">
         <v>45090.0</v>
@@ -1321,28 +1321,28 @@
         <v>36.8</v>
       </c>
       <c r="C32" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="D32" t="n">
-        <v>44.2</v>
+        <v>44.7</v>
       </c>
       <c r="E32" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="F32" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="G32" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="H32" t="n">
-        <v>49.2</v>
+        <v>48.6</v>
       </c>
       <c r="I32" t="n">
         <v>51.6</v>
       </c>
       <c r="J32" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="K32" t="n" s="2">
         <v>45090.0</v>
@@ -1356,31 +1356,31 @@
         <v>15</v>
       </c>
       <c r="B33" t="n">
-        <v>45.0</v>
+        <v>44.7</v>
       </c>
       <c r="C33" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="D33" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
       <c r="E33" t="n">
-        <v>48.4</v>
+        <v>48.8</v>
       </c>
       <c r="F33" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="G33" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="H33" t="n">
-        <v>49.4</v>
+        <v>51.1</v>
       </c>
       <c r="I33" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="J33" t="n">
-        <v>53.7</v>
+        <v>54.0</v>
       </c>
       <c r="K33" t="n" s="2">
         <v>45090.0</v>
@@ -1394,31 +1394,31 @@
         <v>16</v>
       </c>
       <c r="B34" t="n">
-        <v>42.0</v>
+        <v>41.8</v>
       </c>
       <c r="C34" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
       </c>
       <c r="E34" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F34" t="n">
         <v>50.1</v>
       </c>
       <c r="G34" t="n">
-        <v>51.1</v>
+        <v>51.0</v>
       </c>
       <c r="H34" t="n">
         <v>51.5</v>
       </c>
       <c r="I34" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="J34" t="n">
-        <v>56.3</v>
+        <v>57.2</v>
       </c>
       <c r="K34" t="n" s="2">
         <v>45090.0</v>
@@ -1432,31 +1432,31 @@
         <v>17</v>
       </c>
       <c r="B35" t="n">
-        <v>36.8</v>
+        <v>36.3</v>
       </c>
       <c r="C35" t="n">
-        <v>39.4</v>
+        <v>39.2</v>
       </c>
       <c r="D35" t="n">
-        <v>42.7</v>
+        <v>42.3</v>
       </c>
       <c r="E35" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="F35" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="G35" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="H35" t="n">
-        <v>58.2</v>
+        <v>57.9</v>
       </c>
       <c r="I35" t="n">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
       <c r="J35" t="n">
-        <v>62.4</v>
+        <v>63.2</v>
       </c>
       <c r="K35" t="n" s="2">
         <v>45090.0</v>
@@ -1470,31 +1470,31 @@
         <v>18</v>
       </c>
       <c r="B36" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="C36" t="n">
-        <v>41.0</v>
+        <v>40.4</v>
       </c>
       <c r="D36" t="n">
         <v>45.2</v>
       </c>
       <c r="E36" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="F36" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="G36" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="H36" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="I36" t="n">
-        <v>50.7</v>
+        <v>51.1</v>
       </c>
       <c r="J36" t="n">
-        <v>52.9</v>
+        <v>53.3</v>
       </c>
       <c r="K36" t="n" s="2">
         <v>45090.0</v>
@@ -1508,13 +1508,13 @@
         <v>19</v>
       </c>
       <c r="B37" t="n">
-        <v>32.1</v>
+        <v>30.4</v>
       </c>
       <c r="C37" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="D37" t="n">
-        <v>49.0</v>
+        <v>49.2</v>
       </c>
       <c r="E37" t="n">
         <v>47.4</v>
@@ -1523,16 +1523,16 @@
         <v>49.5</v>
       </c>
       <c r="G37" t="n">
-        <v>50.9</v>
+        <v>51.0</v>
       </c>
       <c r="H37" t="n">
-        <v>51.3</v>
+        <v>52.2</v>
       </c>
       <c r="I37" t="n">
-        <v>56.8</v>
+        <v>57.0</v>
       </c>
       <c r="J37" t="n">
-        <v>63.2</v>
+        <v>64.7</v>
       </c>
       <c r="K37" t="n" s="2">
         <v>45090.0</v>
@@ -1546,16 +1546,16 @@
         <v>20</v>
       </c>
       <c r="B38" t="n">
-        <v>36.8</v>
+        <v>36.3</v>
       </c>
       <c r="C38" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="D38" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="E38" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="F38" t="n">
         <v>50.4</v>
@@ -1564,13 +1564,13 @@
         <v>51.3</v>
       </c>
       <c r="H38" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="I38" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="J38" t="n">
-        <v>62.1</v>
+        <v>62.8</v>
       </c>
       <c r="K38" t="n" s="2">
         <v>45090.0</v>
@@ -1587,28 +1587,28 @@
         <v>40.8</v>
       </c>
       <c r="C39" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="D39" t="n">
-        <v>42.7</v>
+        <v>43.2</v>
       </c>
       <c r="E39" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F39" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="G39" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="H39" t="n">
-        <v>57.7</v>
+        <v>57.2</v>
       </c>
       <c r="I39" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="J39" t="n">
-        <v>60.0</v>
+        <v>60.2</v>
       </c>
       <c r="K39" t="n" s="2">
         <v>45090.0</v>
@@ -1622,31 +1622,31 @@
         <v>22</v>
       </c>
       <c r="B40" t="n">
-        <v>34.8</v>
+        <v>32.9</v>
       </c>
       <c r="C40" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="D40" t="n">
-        <v>46.7</v>
+        <v>47.2</v>
       </c>
       <c r="E40" t="n">
-        <v>47.5</v>
+        <v>47.0</v>
       </c>
       <c r="F40" t="n">
         <v>48.8</v>
       </c>
       <c r="G40" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="H40" t="n">
-        <v>53.0</v>
+        <v>52.9</v>
       </c>
       <c r="I40" t="n">
-        <v>56.0</v>
+        <v>56.2</v>
       </c>
       <c r="J40" t="n">
-        <v>60.0</v>
+        <v>61.7</v>
       </c>
       <c r="K40" t="n" s="2">
         <v>45090.0</v>
@@ -1660,31 +1660,31 @@
         <v>12</v>
       </c>
       <c r="B41" t="n">
-        <v>38.8</v>
+        <v>37.8</v>
       </c>
       <c r="C41" t="n">
-        <v>44.2</v>
+        <v>43.7</v>
       </c>
       <c r="D41" t="n">
         <v>49.2</v>
       </c>
       <c r="E41" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="F41" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="G41" t="n">
         <v>51.0</v>
       </c>
       <c r="H41" t="n">
-        <v>51.2</v>
+        <v>51.0</v>
       </c>
       <c r="I41" t="n">
-        <v>54.1</v>
+        <v>54.3</v>
       </c>
       <c r="J41" t="n">
-        <v>57.8</v>
+        <v>58.0</v>
       </c>
       <c r="K41" t="n" s="2">
         <v>45130.0</v>
@@ -1698,31 +1698,31 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>42.7</v>
+        <v>42.3</v>
       </c>
       <c r="C42" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="D42" t="n">
-        <v>46.5</v>
+        <v>46.2</v>
       </c>
       <c r="E42" t="n">
-        <v>50.0</v>
+        <v>49.8</v>
       </c>
       <c r="F42" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="G42" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="H42" t="n">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="I42" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="J42" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="K42" t="n" s="2">
         <v>45130.0</v>
@@ -1736,31 +1736,31 @@
         <v>14</v>
       </c>
       <c r="B43" t="n">
-        <v>39.0</v>
+        <v>39.3</v>
       </c>
       <c r="C43" t="n">
-        <v>43.8</v>
+        <v>44.2</v>
       </c>
       <c r="D43" t="n">
-        <v>47.9</v>
+        <v>48.2</v>
       </c>
       <c r="E43" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="F43" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="G43" t="n">
         <v>50.8</v>
       </c>
       <c r="H43" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="I43" t="n">
-        <v>55.4</v>
+        <v>55.1</v>
       </c>
       <c r="J43" t="n">
-        <v>58.7</v>
+        <v>58.5</v>
       </c>
       <c r="K43" t="n" s="2">
         <v>45130.0</v>
@@ -1774,19 +1774,19 @@
         <v>15</v>
       </c>
       <c r="B44" t="n">
-        <v>37.3</v>
+        <v>38.8</v>
       </c>
       <c r="C44" t="n">
-        <v>45.1</v>
+        <v>45.5</v>
       </c>
       <c r="D44" t="n">
-        <v>49.2</v>
+        <v>49.7</v>
       </c>
       <c r="E44" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="F44" t="n">
-        <v>51.0</v>
+        <v>51.1</v>
       </c>
       <c r="G44" t="n">
         <v>51.9</v>
@@ -1795,10 +1795,10 @@
         <v>53.0</v>
       </c>
       <c r="I44" t="n">
-        <v>56.0</v>
+        <v>55.8</v>
       </c>
       <c r="J44" t="n">
-        <v>60.7</v>
+        <v>61.0</v>
       </c>
       <c r="K44" t="n" s="2">
         <v>45130.0</v>
@@ -1812,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="B45" t="n">
-        <v>39.0</v>
+        <v>38.8</v>
       </c>
       <c r="C45" t="n">
         <v>42.7</v>
@@ -1821,22 +1821,22 @@
         <v>49.2</v>
       </c>
       <c r="E45" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F45" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="G45" t="n">
-        <v>53.6</v>
+        <v>53.4</v>
       </c>
       <c r="H45" t="n">
         <v>51.8</v>
       </c>
       <c r="I45" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="J45" t="n">
-        <v>63.8</v>
+        <v>64.2</v>
       </c>
       <c r="K45" t="n" s="2">
         <v>45130.0</v>
@@ -1853,28 +1853,28 @@
         <v>37.8</v>
       </c>
       <c r="C46" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="D46" t="n">
-        <v>45.2</v>
+        <v>44.7</v>
       </c>
       <c r="E46" t="n">
         <v>49.7</v>
       </c>
       <c r="F46" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="G46" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="H46" t="n">
-        <v>55.9</v>
+        <v>56.4</v>
       </c>
       <c r="I46" t="n">
         <v>59.1</v>
       </c>
       <c r="J46" t="n">
-        <v>62.3</v>
+        <v>62.4</v>
       </c>
       <c r="K46" t="n" s="2">
         <v>45130.0</v>
@@ -1888,13 +1888,13 @@
         <v>18</v>
       </c>
       <c r="B47" t="n">
-        <v>34.6</v>
+        <v>35.3</v>
       </c>
       <c r="C47" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="D47" t="n">
-        <v>44.3</v>
+        <v>45.7</v>
       </c>
       <c r="E47" t="n">
         <v>46.1</v>
@@ -1903,16 +1903,16 @@
         <v>47.6</v>
       </c>
       <c r="G47" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="H47" t="n">
-        <v>52.1</v>
+        <v>51.5</v>
       </c>
       <c r="I47" t="n">
-        <v>54.7</v>
+        <v>54.5</v>
       </c>
       <c r="J47" t="n">
-        <v>57.3</v>
+        <v>57.6</v>
       </c>
       <c r="K47" t="n" s="2">
         <v>45130.0</v>
@@ -1929,25 +1929,25 @@
         <v>45.7</v>
       </c>
       <c r="C48" t="n">
-        <v>49.0</v>
+        <v>49.1</v>
       </c>
       <c r="D48" t="n">
         <v>52.1</v>
       </c>
       <c r="E48" t="n">
-        <v>52.0</v>
+        <v>52.3</v>
       </c>
       <c r="F48" t="n">
         <v>53.6</v>
       </c>
       <c r="G48" t="n">
-        <v>55.3</v>
+        <v>55.6</v>
       </c>
       <c r="H48" t="n">
         <v>53.6</v>
       </c>
       <c r="I48" t="n">
-        <v>57.0</v>
+        <v>56.9</v>
       </c>
       <c r="J48" t="n">
         <v>61.2</v>
@@ -1964,16 +1964,16 @@
         <v>20</v>
       </c>
       <c r="B49" t="n">
-        <v>42.0</v>
+        <v>41.3</v>
       </c>
       <c r="C49" t="n">
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
       <c r="D49" t="n">
-        <v>48.2</v>
+        <v>48.7</v>
       </c>
       <c r="E49" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
       <c r="F49" t="n">
         <v>54.3</v>
@@ -1982,13 +1982,13 @@
         <v>55.7</v>
       </c>
       <c r="H49" t="n">
-        <v>59.7</v>
+        <v>59.4</v>
       </c>
       <c r="I49" t="n">
-        <v>62.1</v>
+        <v>62.3</v>
       </c>
       <c r="J49" t="n">
-        <v>64.6</v>
+        <v>65.3</v>
       </c>
       <c r="K49" t="n" s="2">
         <v>45130.0</v>
@@ -2002,31 +2002,31 @@
         <v>21</v>
       </c>
       <c r="B50" t="n">
-        <v>41.0</v>
+        <v>40.8</v>
       </c>
       <c r="C50" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="D50" t="n">
         <v>44.7</v>
       </c>
       <c r="E50" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
       <c r="F50" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="G50" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="H50" t="n">
-        <v>55.6</v>
+        <v>56.1</v>
       </c>
       <c r="I50" t="n">
-        <v>58.8</v>
+        <v>59.0</v>
       </c>
       <c r="J50" t="n">
-        <v>61.0</v>
+        <v>61.2</v>
       </c>
       <c r="K50" t="n" s="2">
         <v>45130.0</v>
@@ -2040,31 +2040,31 @@
         <v>22</v>
       </c>
       <c r="B51" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="C51" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="D51" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
       <c r="E51" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F51" t="n">
         <v>51.2</v>
       </c>
       <c r="G51" t="n">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
       <c r="H51" t="n">
-        <v>54.6</v>
+        <v>54.4</v>
       </c>
       <c r="I51" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="J51" t="n">
-        <v>63.3</v>
+        <v>63.0</v>
       </c>
       <c r="K51" t="n" s="2">
         <v>45130.0</v>
@@ -2078,31 +2078,31 @@
         <v>12</v>
       </c>
       <c r="B52" t="n">
-        <v>32.1</v>
+        <v>30.4</v>
       </c>
       <c r="C52" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="D52" t="n">
-        <v>48.2</v>
+        <v>47.7</v>
       </c>
       <c r="E52" t="n">
-        <v>44.4</v>
+        <v>44.0</v>
       </c>
       <c r="F52" t="n">
-        <v>47.3</v>
+        <v>47.0</v>
       </c>
       <c r="G52" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="H52" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="I52" t="n">
-        <v>52.6</v>
+        <v>53.0</v>
       </c>
       <c r="J52" t="n">
-        <v>56.8</v>
+        <v>58.4</v>
       </c>
       <c r="K52" t="n" s="2">
         <v>45180.0</v>
@@ -2116,19 +2116,19 @@
         <v>13</v>
       </c>
       <c r="B53" t="n">
-        <v>43.7</v>
+        <v>43.2</v>
       </c>
       <c r="C53" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="D53" t="n">
         <v>50.2</v>
       </c>
       <c r="E53" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="F53" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
       <c r="G53" t="n">
         <v>53.0</v>
@@ -2140,7 +2140,7 @@
         <v>57.0</v>
       </c>
       <c r="J53" t="n">
-        <v>59.9</v>
+        <v>60.6</v>
       </c>
       <c r="K53" t="n" s="2">
         <v>45180.0</v>
@@ -2154,31 +2154,31 @@
         <v>14</v>
       </c>
       <c r="B54" t="n">
-        <v>28.4</v>
+        <v>27.4</v>
       </c>
       <c r="C54" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="D54" t="n">
-        <v>44.0</v>
+        <v>45.2</v>
       </c>
       <c r="E54" t="n">
         <v>44.2</v>
       </c>
       <c r="F54" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="G54" t="n">
         <v>48.3</v>
       </c>
       <c r="H54" t="n">
-        <v>51.9</v>
+        <v>50.7</v>
       </c>
       <c r="I54" t="n">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="J54" t="n">
-        <v>60.1</v>
+        <v>60.4</v>
       </c>
       <c r="K54" t="n" s="2">
         <v>45180.0</v>
@@ -2192,31 +2192,31 @@
         <v>15</v>
       </c>
       <c r="B55" t="n">
-        <v>45.7</v>
+        <v>45.2</v>
       </c>
       <c r="C55" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="D55" t="n">
         <v>50.2</v>
       </c>
       <c r="E55" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="F55" t="n">
         <v>52.0</v>
       </c>
       <c r="G55" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="H55" t="n">
-        <v>54.1</v>
+        <v>54.3</v>
       </c>
       <c r="I55" t="n">
-        <v>56.0</v>
+        <v>56.1</v>
       </c>
       <c r="J55" t="n">
-        <v>58.1</v>
+        <v>58.4</v>
       </c>
       <c r="K55" t="n" s="2">
         <v>45180.0</v>
@@ -2233,28 +2233,28 @@
         <v>45.2</v>
       </c>
       <c r="C56" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="D56" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
       <c r="E56" t="n">
         <v>50.4</v>
       </c>
       <c r="F56" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="G56" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="H56" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
       <c r="I56" t="n">
         <v>54.4</v>
       </c>
       <c r="J56" t="n">
-        <v>56.7</v>
+        <v>56.5</v>
       </c>
       <c r="K56" t="n" s="2">
         <v>45180.0</v>
@@ -2268,7 +2268,7 @@
         <v>17</v>
       </c>
       <c r="B57" t="n">
-        <v>40.3</v>
+        <v>39.3</v>
       </c>
       <c r="C57" t="n">
         <v>42.5</v>
@@ -2277,22 +2277,22 @@
         <v>44.7</v>
       </c>
       <c r="E57" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="F57" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="G57" t="n">
         <v>51.0</v>
       </c>
       <c r="H57" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="I57" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="J57" t="n">
-        <v>59.5</v>
+        <v>59.3</v>
       </c>
       <c r="K57" t="n" s="2">
         <v>45180.0</v>
@@ -2309,28 +2309,28 @@
         <v>23.0</v>
       </c>
       <c r="C58" t="n">
-        <v>27.5</v>
+        <v>27.8</v>
       </c>
       <c r="D58" t="n">
-        <v>42.0</v>
+        <v>42.7</v>
       </c>
       <c r="E58" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="F58" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="G58" t="n">
-        <v>45.0</v>
+        <v>45.7</v>
       </c>
       <c r="H58" t="n">
-        <v>50.6</v>
+        <v>49.0</v>
       </c>
       <c r="I58" t="n">
-        <v>56.3</v>
+        <v>55.9</v>
       </c>
       <c r="J58" t="n">
-        <v>63.0</v>
+        <v>62.4</v>
       </c>
       <c r="K58" t="n" s="2">
         <v>45180.0</v>
@@ -2344,31 +2344,31 @@
         <v>19</v>
       </c>
       <c r="B59" t="n">
-        <v>29.2</v>
+        <v>28.4</v>
       </c>
       <c r="C59" t="n">
-        <v>39.8</v>
+        <v>41.0</v>
       </c>
       <c r="D59" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="E59" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="F59" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="G59" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="H59" t="n">
-        <v>54.8</v>
+        <v>54.2</v>
       </c>
       <c r="I59" t="n">
-        <v>61.5</v>
+        <v>60.9</v>
       </c>
       <c r="J59" t="n">
-        <v>68.6</v>
+        <v>69.7</v>
       </c>
       <c r="K59" t="n" s="2">
         <v>45180.0</v>
@@ -2382,7 +2382,7 @@
         <v>20</v>
       </c>
       <c r="B60" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="C60" t="n">
         <v>43.5</v>
@@ -2397,13 +2397,13 @@
         <v>52.2</v>
       </c>
       <c r="G60" t="n">
-        <v>52.7</v>
+        <v>52.9</v>
       </c>
       <c r="H60" t="n">
-        <v>57.8</v>
+        <v>58.4</v>
       </c>
       <c r="I60" t="n">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
       <c r="J60" t="n">
         <v>62.1</v>
@@ -2420,31 +2420,31 @@
         <v>21</v>
       </c>
       <c r="B61" t="n">
-        <v>43.0</v>
+        <v>42.7</v>
       </c>
       <c r="C61" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="D61" t="n">
-        <v>45.7</v>
+        <v>45.2</v>
       </c>
       <c r="E61" t="n">
-        <v>50.1</v>
+        <v>50.0</v>
       </c>
       <c r="F61" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="G61" t="n">
         <v>51.3</v>
       </c>
       <c r="H61" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="I61" t="n">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="J61" t="n">
-        <v>57.3</v>
+        <v>57.8</v>
       </c>
       <c r="K61" t="n" s="2">
         <v>45180.0</v>
@@ -2461,28 +2461,28 @@
         <v>23.0</v>
       </c>
       <c r="C62" t="n">
-        <v>34.0</v>
+        <v>33.3</v>
       </c>
       <c r="D62" t="n">
-        <v>51.5</v>
+        <v>50.9</v>
       </c>
       <c r="E62" t="n">
         <v>43.7</v>
       </c>
       <c r="F62" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="G62" t="n">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
       <c r="H62" t="n">
-        <v>54.0</v>
+        <v>53.9</v>
       </c>
       <c r="I62" t="n">
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
       <c r="J62" t="n">
-        <v>86.4</v>
+        <v>85.7</v>
       </c>
       <c r="K62" t="n" s="2">
         <v>45180.0</v>

--- a/data/crit_values_final.xlsx
+++ b/data/crit_values_final.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2383814C-5D4C-BB49-9F07-C938A9D84468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -80,22 +88,22 @@
     <t>Quercus montana</t>
   </si>
   <si>
-    <t>Ulmus americana</t>
+    <t>TN</t>
   </si>
   <si>
-    <t>TN</t>
+    <t>Ulmus rubra</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,7 +115,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -122,20 +130,331 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -173,2325 +492,2325 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>43.2</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>47.3</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>51.1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>50.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>51.8</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>52.5</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>53.4</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>55.7</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>58.9</v>
       </c>
-      <c r="K2" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K2" s="1">
+        <v>44733</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>41.3</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>44.8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>47.7</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>51.1</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>52.2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>53.7</v>
       </c>
-      <c r="H3" t="n">
-        <v>55.0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3">
+        <v>55</v>
+      </c>
+      <c r="I3">
         <v>58.8</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>63.5</v>
       </c>
-      <c r="K3" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K3" s="1">
+        <v>44733</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>41.8</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>44.3</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>46.7</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>50.8</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>51.9</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>53.5</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>54.7</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>58.7</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>62.9</v>
       </c>
-      <c r="K4" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K4" s="1">
+        <v>44733</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="C5">
         <v>42.5</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>45.2</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>50.9</v>
       </c>
-      <c r="F5" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5">
+        <v>52</v>
+      </c>
+      <c r="G5">
         <v>53.3</v>
       </c>
-      <c r="H5" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="H5">
+        <v>57</v>
+      </c>
+      <c r="I5">
         <v>60.4</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>63.9</v>
       </c>
-      <c r="K5" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K5" s="1">
+        <v>44733</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="C6">
         <v>43.5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>47.2</v>
       </c>
-      <c r="E6" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6">
+        <v>51</v>
+      </c>
+      <c r="F6">
         <v>52.4</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>54.1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>56.2</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>60.3</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>64.3</v>
       </c>
-      <c r="K6" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K6" s="1">
+        <v>44733</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="C7">
         <v>43.4</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>46.7</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>49.7</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>50.8</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>52.2</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>53.7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>57.3</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>61.7</v>
       </c>
-      <c r="K7" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K7" s="1">
+        <v>44733</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>42.3</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>44.5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>46.7</v>
       </c>
-      <c r="E8" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>51</v>
+      </c>
+      <c r="G8">
         <v>52.2</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>53.2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>56.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>60.4</v>
       </c>
-      <c r="K8" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K8" s="1">
+        <v>44733</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="C9">
         <v>42.6</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>45.2</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>50.6</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>51.6</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>52.5</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>57.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>59.9</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>62.4</v>
       </c>
-      <c r="K9" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K9" s="1">
+        <v>44733</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>44.7</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>46.5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>48.7</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>52.8</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>53.9</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>55.2</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>57.8</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>60.8</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>63.6</v>
       </c>
-      <c r="K10" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K10" s="1">
+        <v>44733</v>
       </c>
       <c r="L10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="C11" t="n">
-        <v>44.0</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="B11">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="C11">
+        <v>44</v>
+      </c>
+      <c r="D11">
         <v>48.2</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>51.9</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>53.5</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>55.2</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>58.6</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>62.2</v>
       </c>
-      <c r="J11" t="n">
-        <v>65.9</v>
-      </c>
-      <c r="K11" t="n" s="2">
-        <v>44733.0</v>
+      <c r="J11">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="K11" s="1">
+        <v>44733</v>
       </c>
       <c r="L11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="C12" t="n">
+      <c r="B12">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="C12">
         <v>40.6</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>46.2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>47.2</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>48.9</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>50.7</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>51.7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>56.5</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>60.9</v>
       </c>
-      <c r="K12" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K12" s="1">
+        <v>44733</v>
       </c>
       <c r="L12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>43.2</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>46.1</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>49.2</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>51.3</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>52.5</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>54.2</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>54.1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>58.2</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>62.8</v>
       </c>
-      <c r="K13" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K13" s="1">
+        <v>44768</v>
       </c>
       <c r="L13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>45.7</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>47.9</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>49.7</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>52.4</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>53.2</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>54.5</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>54.9</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>57.9</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>61.9</v>
       </c>
-      <c r="K14" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K14" s="1">
+        <v>44768</v>
       </c>
       <c r="L14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>45.2</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>47.9</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>50.2</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>51.8</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>52.8</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>54.1</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>54.6</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>57.1</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>60.5</v>
       </c>
-      <c r="K15" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K15" s="1">
+        <v>44768</v>
       </c>
       <c r="L15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>44.2</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>47.5</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>51.1</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>52.5</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>53.7</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>54.9</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>54.5</v>
       </c>
-      <c r="I16" t="n">
-        <v>59.0</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="I16">
+        <v>59</v>
+      </c>
+      <c r="J16">
         <v>62.5</v>
       </c>
-      <c r="K16" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K16" s="1">
+        <v>44768</v>
       </c>
       <c r="L16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>44.2</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>46.2</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>48.7</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>52.9</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>54.3</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>55.5</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>58.2</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>61.6</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>64.2</v>
       </c>
-      <c r="K17" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K17" s="1">
+        <v>44768</v>
       </c>
       <c r="L17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>41.8</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>44.2</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>47.2</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>51.6</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>52.5</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>53.3</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>57.2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>59.7</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>62.5</v>
       </c>
-      <c r="K18" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K18" s="1">
+        <v>44768</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>47.2</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>48.5</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>50.2</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>51.1</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>51.8</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>52.7</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>53.1</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>54.7</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>55.9</v>
       </c>
-      <c r="K19" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K19" s="1">
+        <v>44768</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>41.8</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>46.3</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>49.7</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>51.2</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>52.2</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>53.7</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>54.4</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>57.6</v>
       </c>
-      <c r="J20" t="n">
-        <v>64.0</v>
-      </c>
-      <c r="K20" t="n" s="2">
-        <v>44768.0</v>
+      <c r="J20">
+        <v>64</v>
+      </c>
+      <c r="K20" s="1">
+        <v>44768</v>
       </c>
       <c r="L20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C21" t="n">
+      <c r="B21">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="C21">
         <v>44.1</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>48.2</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>54.3</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>56.1</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>59.7</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>60.6</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>66.7</v>
       </c>
-      <c r="J21" t="n">
-        <v>77.9</v>
-      </c>
-      <c r="K21" t="n" s="2">
-        <v>44768.0</v>
+      <c r="J21">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="K21" s="1">
+        <v>44768</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="C22" t="n">
+      <c r="B22">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="C22">
         <v>43.9</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>47.7</v>
       </c>
-      <c r="E22" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="E22">
+        <v>52</v>
+      </c>
+      <c r="F22">
+        <v>53</v>
+      </c>
+      <c r="G22">
         <v>55.2</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>56.6</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>60.9</v>
       </c>
-      <c r="J22" t="n">
-        <v>70.4</v>
-      </c>
-      <c r="K22" t="n" s="2">
-        <v>44768.0</v>
+      <c r="J22">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="K22" s="1">
+        <v>44768</v>
       </c>
       <c r="L22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>43.2</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>47.5</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>50.6</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>52.5</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>53.5</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>54.8</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>55.3</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>59.1</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>63.1</v>
       </c>
-      <c r="K23" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K23" s="1">
+        <v>44768</v>
       </c>
       <c r="L23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>12</v>
       </c>
-      <c r="B24" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C24" t="n">
+      <c r="B24">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="C24">
         <v>41.6</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>45.2</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>48.1</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>49.1</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>50.4</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>52.3</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>55.7</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>60.2</v>
       </c>
-      <c r="K24" t="n" s="2">
-        <v>45063.0</v>
+      <c r="K24" s="1">
+        <v>45063</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>14</v>
       </c>
-      <c r="B25" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C25" t="n">
+      <c r="B25">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="C25">
         <v>42.5</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>46.2</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>47.5</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>48.6</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>49.8</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>50.1</v>
       </c>
-      <c r="I25" t="n">
-        <v>54.0</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I25">
+        <v>54</v>
+      </c>
+      <c r="J25">
         <v>59.5</v>
       </c>
-      <c r="K25" t="n" s="2">
-        <v>45063.0</v>
+      <c r="K25" s="1">
+        <v>45063</v>
       </c>
       <c r="L25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="C26" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="B26">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="C26">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="D26">
         <v>43.2</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>48.8</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>49.7</v>
       </c>
-      <c r="G26" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="G26">
+        <v>51</v>
+      </c>
+      <c r="H26">
         <v>54.6</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>58.1</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>62.6</v>
       </c>
-      <c r="K26" t="n" s="2">
-        <v>45063.0</v>
+      <c r="K26" s="1">
+        <v>45063</v>
       </c>
       <c r="L26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>42.3</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>45.5</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>47.7</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>47.7</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>48.8</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>49.7</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>49.4</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>51.9</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>54.2</v>
       </c>
-      <c r="K27" t="n" s="2">
-        <v>45077.0</v>
+      <c r="K27" s="1">
+        <v>45077</v>
       </c>
       <c r="L27" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>14</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>42.3</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>43.6</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>45.2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>47.8</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>48.4</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>49.1</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>50.9</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>52.6</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>54.1</v>
       </c>
-      <c r="K28" t="n" s="2">
-        <v>45077.0</v>
+      <c r="K28" s="1">
+        <v>45077</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>17</v>
       </c>
-      <c r="B29" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="C29" t="n">
+      <c r="B29">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C29">
         <v>40.6</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>43.2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>48.4</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>49.3</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>50.1</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>55.1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>56.9</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>58.9</v>
       </c>
-      <c r="K29" t="n" s="2">
-        <v>45077.0</v>
+      <c r="K29" s="1">
+        <v>45077</v>
       </c>
       <c r="L29" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>41.3</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>43.7</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>48.2</v>
       </c>
-      <c r="E30" t="n">
-        <v>48.0</v>
-      </c>
-      <c r="F30" t="n">
+      <c r="E30">
+        <v>48</v>
+      </c>
+      <c r="F30">
         <v>49.2</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>50.6</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>52.3</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>54.2</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>55.9</v>
       </c>
-      <c r="K30" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K30" s="1">
+        <v>45090</v>
       </c>
       <c r="L30" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>13</v>
       </c>
-      <c r="B31" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="C31" t="n">
+      <c r="B31">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="C31">
         <v>42.4</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>45.7</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>49.6</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>50.4</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>51.1</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>55.6</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>57.5</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>59.6</v>
       </c>
-      <c r="K31" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K31" s="1">
+        <v>45090</v>
       </c>
       <c r="L31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>14</v>
       </c>
-      <c r="B32" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="C32" t="n">
+      <c r="B32">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="C32">
         <v>41.1</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>44.7</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>45.3</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>46.4</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>47.3</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>48.6</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>51.6</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32">
         <v>54.2</v>
       </c>
-      <c r="K32" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K32" s="1">
+        <v>45090</v>
       </c>
       <c r="L32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>15</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>44.7</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>46.4</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>49.2</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>48.8</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>49.8</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>50.7</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33">
         <v>51.1</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>52.7</v>
       </c>
-      <c r="J33" t="n">
-        <v>54.0</v>
-      </c>
-      <c r="K33" t="n" s="2">
-        <v>45090.0</v>
+      <c r="J33">
+        <v>54</v>
+      </c>
+      <c r="K33" s="1">
+        <v>45090</v>
       </c>
       <c r="L33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>16</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>41.8</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>45.3</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>49.2</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>48.9</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>50.1</v>
       </c>
-      <c r="G34" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="G34">
+        <v>51</v>
+      </c>
+      <c r="H34">
         <v>51.5</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>54.5</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34">
         <v>57.2</v>
       </c>
-      <c r="K34" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K34" s="1">
+        <v>45090</v>
       </c>
       <c r="L34" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>17</v>
       </c>
-      <c r="B35" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="C35" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="B35">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="C35">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="D35">
         <v>42.3</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>49.3</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>50.4</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>51.5</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>57.9</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35">
         <v>60.2</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35">
         <v>63.2</v>
       </c>
-      <c r="K35" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K35" s="1">
+        <v>45090</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>18</v>
       </c>
-      <c r="B36" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="C36" t="n">
+      <c r="B36">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="C36">
         <v>40.4</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>45.2</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>44.6</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>45.9</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>47.3</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>48.6</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>51.1</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36">
         <v>53.3</v>
       </c>
-      <c r="K36" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K36" s="1">
+        <v>45090</v>
       </c>
       <c r="L36" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>19</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>30.4</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>42.2</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>49.2</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>47.4</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>49.5</v>
       </c>
-      <c r="G37" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="G37">
+        <v>51</v>
+      </c>
+      <c r="H37">
         <v>52.2</v>
       </c>
-      <c r="I37" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="J37" t="n">
+      <c r="I37">
+        <v>57</v>
+      </c>
+      <c r="J37">
         <v>64.7</v>
       </c>
-      <c r="K37" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K37" s="1">
+        <v>45090</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>20</v>
       </c>
-      <c r="B38" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="C38" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="D38" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="E38" t="n">
+      <c r="B38">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="C38">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="D38">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E38">
         <v>49.6</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>50.4</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>51.3</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38">
         <v>58.2</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38">
         <v>60.5</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38">
         <v>62.8</v>
       </c>
-      <c r="K38" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K38" s="1">
+        <v>45090</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>21</v>
       </c>
-      <c r="B39" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="C39" t="n">
+      <c r="B39">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="C39">
         <v>41.9</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>43.2</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>50.4</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>50.8</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>51.3</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39">
         <v>57.2</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39">
         <v>58.8</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39">
         <v>60.2</v>
       </c>
-      <c r="K39" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K39" s="1">
+        <v>45090</v>
       </c>
       <c r="L39" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>22</v>
-      </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>32.9</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>41.2</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>47.2</v>
       </c>
-      <c r="E40" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="F40" t="n">
+      <c r="E40">
+        <v>47</v>
+      </c>
+      <c r="F40">
         <v>48.8</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>50.4</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40">
         <v>52.9</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40">
         <v>56.2</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40">
         <v>61.7</v>
       </c>
-      <c r="K40" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K40" s="1">
+        <v>45090</v>
       </c>
       <c r="L40" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>12</v>
       </c>
-      <c r="B41" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C41" t="n">
+      <c r="B41">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="C41">
         <v>43.7</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>49.2</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>47.7</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>49.5</v>
       </c>
-      <c r="G41" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="I41" t="n">
+      <c r="G41">
+        <v>51</v>
+      </c>
+      <c r="H41">
+        <v>51</v>
+      </c>
+      <c r="I41">
         <v>54.3</v>
       </c>
-      <c r="J41" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="K41" t="n" s="2">
-        <v>45130.0</v>
+      <c r="J41">
+        <v>58</v>
+      </c>
+      <c r="K41" s="1">
+        <v>45130</v>
       </c>
       <c r="L41" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>13</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>42.3</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>44.4</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>46.2</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>49.8</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>50.4</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42">
         <v>50.9</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42">
         <v>54.2</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42">
         <v>55.8</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42">
         <v>57.2</v>
       </c>
-      <c r="K42" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K42" s="1">
+        <v>45130</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>14</v>
       </c>
-      <c r="B43" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="C43" t="n">
+      <c r="B43">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="C43">
         <v>44.2</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>48.2</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>48.6</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>49.8</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>50.8</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43">
         <v>52.9</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43">
         <v>55.1</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43">
         <v>58.5</v>
       </c>
-      <c r="K43" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K43" s="1">
+        <v>45130</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>15</v>
       </c>
-      <c r="B44" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="C44" t="n">
+      <c r="B44">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="C44">
         <v>45.5</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>49.7</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>49.9</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>51.1</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>51.9</v>
       </c>
-      <c r="H44" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="I44" t="n">
+      <c r="H44">
+        <v>53</v>
+      </c>
+      <c r="I44">
         <v>55.8</v>
       </c>
-      <c r="J44" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="K44" t="n" s="2">
-        <v>45130.0</v>
+      <c r="J44">
+        <v>61</v>
+      </c>
+      <c r="K44" s="1">
+        <v>45130</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>16</v>
       </c>
-      <c r="B45" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="C45" t="n">
+      <c r="B45">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="C45">
         <v>42.7</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>49.2</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>50.3</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>51.6</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>53.4</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45">
         <v>51.8</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45">
         <v>59.6</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45">
         <v>64.2</v>
       </c>
-      <c r="K45" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K45" s="1">
+        <v>45130</v>
       </c>
       <c r="L45" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>17</v>
       </c>
-      <c r="B46" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C46" t="n">
+      <c r="B46">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="C46">
         <v>41.2</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>44.7</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>49.7</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>50.6</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>51.6</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46">
         <v>56.4</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46">
         <v>59.1</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J46">
         <v>62.4</v>
       </c>
-      <c r="K46" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K46" s="1">
+        <v>45130</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>18</v>
       </c>
-      <c r="B47" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="C47" t="n">
+      <c r="B47">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="C47">
         <v>39.9</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>45.7</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>46.1</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>47.6</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>49.2</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47">
         <v>51.5</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47">
         <v>54.5</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47">
         <v>57.6</v>
       </c>
-      <c r="K47" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K47" s="1">
+        <v>45130</v>
       </c>
       <c r="L47" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>19</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>45.7</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>49.1</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>52.1</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>52.3</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>53.6</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48">
         <v>55.6</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48">
         <v>53.6</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48">
         <v>56.9</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48">
         <v>61.2</v>
       </c>
-      <c r="K48" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K48" s="1">
+        <v>45130</v>
       </c>
       <c r="L48" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>20</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>41.3</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>44.8</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>48.7</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>52.8</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>54.3</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49">
         <v>55.7</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49">
         <v>59.4</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49">
         <v>62.3</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49">
         <v>65.3</v>
       </c>
-      <c r="K49" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K49" s="1">
+        <v>45130</v>
       </c>
       <c r="L49" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>21</v>
       </c>
-      <c r="B50" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="C50" t="n">
+      <c r="B50">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="C50">
         <v>42.8</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>44.7</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>50.6</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>51.5</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>52.4</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50">
         <v>56.1</v>
       </c>
-      <c r="I50" t="n">
-        <v>59.0</v>
-      </c>
-      <c r="J50" t="n">
+      <c r="I50">
+        <v>59</v>
+      </c>
+      <c r="J50">
         <v>61.2</v>
       </c>
-      <c r="K50" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K50" s="1">
+        <v>45130</v>
       </c>
       <c r="L50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>22</v>
-      </c>
-      <c r="B51" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="C51" t="n">
+      <c r="B51">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="C51">
         <v>43.9</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>50.6</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>49.8</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>51.2</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51">
         <v>52.7</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51">
         <v>54.4</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>58.2</v>
       </c>
-      <c r="J51" t="n">
-        <v>63.0</v>
-      </c>
-      <c r="K51" t="n" s="2">
-        <v>45130.0</v>
+      <c r="J51">
+        <v>63</v>
+      </c>
+      <c r="K51" s="1">
+        <v>45130</v>
       </c>
       <c r="L51" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>12</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>30.4</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>41.2</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>47.7</v>
       </c>
-      <c r="E52" t="n">
-        <v>44.0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="G52" t="n">
+      <c r="E52">
+        <v>44</v>
+      </c>
+      <c r="F52">
+        <v>47</v>
+      </c>
+      <c r="G52">
         <v>49.3</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52">
         <v>49.6</v>
       </c>
-      <c r="I52" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="J52" t="n">
+      <c r="I52">
+        <v>53</v>
+      </c>
+      <c r="J52">
         <v>58.4</v>
       </c>
-      <c r="K52" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K52" s="1">
+        <v>45180</v>
       </c>
       <c r="L52" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>13</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>43.2</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>47.4</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>50.2</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>51.8</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>52.5</v>
       </c>
-      <c r="G53" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="H53" t="n">
+      <c r="G53">
+        <v>53</v>
+      </c>
+      <c r="H53">
         <v>55.2</v>
       </c>
-      <c r="I53" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="I53">
+        <v>57</v>
+      </c>
+      <c r="J53">
         <v>60.6</v>
       </c>
-      <c r="K53" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K53" s="1">
+        <v>45180</v>
       </c>
       <c r="L53" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>14</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>27.4</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>38.6</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>45.2</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>44.2</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>46.5</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54">
         <v>48.3</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54">
         <v>50.7</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>54.6</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54">
         <v>60.4</v>
       </c>
-      <c r="K54" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K54" s="1">
+        <v>45180</v>
       </c>
       <c r="L54" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>15</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>45.2</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>47.5</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>50.2</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>51.4</v>
       </c>
-      <c r="F55" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="F55">
+        <v>52</v>
+      </c>
+      <c r="G55">
         <v>52.5</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55">
         <v>54.3</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55">
         <v>56.1</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J55">
         <v>58.4</v>
       </c>
-      <c r="K55" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K55" s="1">
+        <v>45180</v>
       </c>
       <c r="L55" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>16</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>45.2</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>47.8</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>50.6</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>50.4</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>51.3</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56">
         <v>52.3</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56">
         <v>52.5</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56">
         <v>54.4</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56">
         <v>56.5</v>
       </c>
-      <c r="K56" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K56" s="1">
+        <v>45180</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>17</v>
       </c>
-      <c r="B57" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="C57" t="n">
+      <c r="B57">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="C57">
         <v>42.5</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>44.7</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>49.2</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>50.1</v>
       </c>
-      <c r="G57" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="H57" t="n">
+      <c r="G57">
+        <v>51</v>
+      </c>
+      <c r="H57">
         <v>54.7</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57">
         <v>56.7</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J57">
         <v>59.3</v>
       </c>
-      <c r="K57" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K57" s="1">
+        <v>45180</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>18</v>
       </c>
-      <c r="B58" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="C58" t="n">
+      <c r="B58">
+        <v>23</v>
+      </c>
+      <c r="C58">
         <v>27.8</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>42.7</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>37.4</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>41.6</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58">
         <v>45.7</v>
       </c>
-      <c r="H58" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="I58" t="n">
+      <c r="H58">
+        <v>49</v>
+      </c>
+      <c r="I58">
         <v>55.9</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58">
         <v>62.4</v>
       </c>
-      <c r="K58" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K58" s="1">
+        <v>45180</v>
       </c>
       <c r="L58" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>19</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>28.4</v>
       </c>
-      <c r="C59" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="D59" t="n">
+      <c r="C59">
+        <v>41</v>
+      </c>
+      <c r="D59">
         <v>50.6</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>50.1</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>52.2</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59">
         <v>53.7</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59">
         <v>54.2</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>60.9</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J59">
         <v>69.7</v>
       </c>
-      <c r="K59" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K59" s="1">
+        <v>45180</v>
       </c>
       <c r="L59" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>20</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>41.7</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>43.5</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>45.2</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>51.5</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>52.2</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60">
         <v>52.9</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60">
         <v>58.4</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60">
         <v>60.2</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J60">
         <v>62.1</v>
       </c>
-      <c r="K60" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K60" s="1">
+        <v>45180</v>
       </c>
       <c r="L60" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>21</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>42.7</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>44.1</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>45.2</v>
       </c>
-      <c r="E61" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="F61" t="n">
+      <c r="E61">
+        <v>50</v>
+      </c>
+      <c r="F61">
         <v>50.6</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61">
         <v>51.3</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61">
         <v>54.6</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61">
         <v>56.3</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J61">
         <v>57.8</v>
       </c>
-      <c r="K61" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K61" s="1">
+        <v>45180</v>
       </c>
       <c r="L61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>22</v>
-      </c>
-      <c r="B62" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="C62" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="D62" t="n">
+      <c r="B62">
+        <v>23</v>
+      </c>
+      <c r="C62">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="D62">
         <v>50.9</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>43.7</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>48.3</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62">
         <v>52.6</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62">
         <v>53.9</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62">
         <v>65.8</v>
       </c>
-      <c r="J62" t="n">
+      <c r="J62">
         <v>85.7</v>
       </c>
-      <c r="K62" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K62" s="1">
+        <v>45180</v>
       </c>
       <c r="L62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>